--- a/daily_matches/job_matches_2026-06-11.xlsx
+++ b/daily_matches/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Infios</t>
+          <t>Class Boxes Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf5414e7655d620</t>
+          <t>https://www.indeed.com/viewjob?jk=10ffab2e7330a09b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Senior Software Development/Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e90415012a94ad70</t>
+          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Quantitative AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Talcott Financial Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jessup, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes, Jenkins, Git, Hadoop</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890d98929cfcbadb</t>
+          <t>https://www.indeed.com/viewjob?jk=f8dfb2afb4c4cdfe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Quantitative AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Talcott Financial Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e1129e4812bf7b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9ae5953bc4e0b5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Inn-Flow Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997076f3557b3e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9dd2a0e256d891</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238647c47b19c8eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cc8aa5b1145a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb941ff0fd6a0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Java Full Stack Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bb07c7a07be0e6</t>
+          <t>https://www.indeed.com/viewjob?jk=38f147ad8d55795a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Axiom Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2b5b0b8e3011dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b276af599e88a7af</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b48f21698f142</t>
+          <t>https://www.indeed.com/viewjob?jk=19137d32d78cfe84</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Redshift, Docker, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f973f7323057e9</t>
+          <t>https://www.indeed.com/viewjob?jk=54b35c879a1bb642</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Kochava</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sandpoint, ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34950007f8bb9798</t>
+          <t>https://www.indeed.com/viewjob?jk=8da2709e8e3a0249</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Product Engineer Data &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Redshift, BigQuery, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ea390592236764</t>
+          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7ea7b918227421</t>
+          <t>https://www.indeed.com/viewjob?jk=395f24178706a394</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee458103ff1c70bf</t>
+          <t>https://www.indeed.com/viewjob?jk=42dc2f786276cd36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Capgemini Invent - Contextual Systems Engineer Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba57da018df901c</t>
+          <t>https://www.indeed.com/viewjob?jk=274253fd583d7c75</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4b77209f1232dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b33c5e3f0585f73f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d73d871e1deea61</t>
+          <t>https://www.indeed.com/viewjob?jk=d490a5e4c58ea8d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47efa737e9fc9146</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c32bcb8a5f4e0f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f05a66307eff77</t>
+          <t>https://www.indeed.com/viewjob?jk=c67e8ee6944e7422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430a6f1d83e30529</t>
+          <t>https://www.indeed.com/viewjob?jk=1723ae89a5522b2d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9980f2267fe92</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3cc2eabeb984da</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54c7515a609d437</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc281ddfed2fedf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97025c53dc8097b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4dbe167ef434fbe</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1424c80ddb92ac16</t>
+          <t>https://www.indeed.com/viewjob?jk=f20c87cd67103293</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f7a92cd47c388f</t>
+          <t>https://www.indeed.com/viewjob?jk=0489c28254bf28c2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a23c7934cd38108</t>
+          <t>https://www.indeed.com/viewjob?jk=4b657969134175f5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11758c6720edfe8c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c9711c1c833a779</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d34a5cd743710</t>
+          <t>https://www.indeed.com/viewjob?jk=9c16bad14518ebb2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fd2bc0f706a630</t>
+          <t>https://www.indeed.com/viewjob?jk=c39d786e572ba861</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52beb77333c9d632</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4e2fb0cb7c99c8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d94aabbffe9af4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c4adb015bcb158</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5882845fc94868</t>
+          <t>https://www.indeed.com/viewjob?jk=30b9d54ecb204c84</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Apache Airflow, Terraform, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=026d02e8ce3baa47</t>
+          <t>https://www.indeed.com/viewjob?jk=f00c9a373cde3271</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Software Development Engineer (Mid Level)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Copilot, Pinecone, Docker, Kubernetes, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ff5ee4ac14175f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc52f5e5cae657fc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Software Engineering SMTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84726e340de9d703</t>
+          <t>https://www.indeed.com/viewjob?jk=3191536a63c5cac7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Sr. Developer - Software Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>RAG, Copilot, S3, EC2, Glue, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,94 +1791,94 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc593c9088c2ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb5cb1b4382c99f2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS MLOps Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, FastAPI, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python</t>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8f53db9ad25323</t>
+          <t>https://www.indeed.com/viewjob?jk=2833a5e5ddb82e5b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Data &amp; AI Platform Architect</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>State of Arizona</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5428d278da22bd02</t>
+          <t>https://www.indeed.com/viewjob?jk=2546b11c9cac9972</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Get Covered LLC</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dbe12e620fc983</t>
+          <t>https://www.indeed.com/viewjob?jk=51f50645dffd57d4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer, Agentic AI Data Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, MLflow, CI/CD, Git, Databricks, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a6e83b8ea37c39</t>
+          <t>https://www.indeed.com/viewjob?jk=f30974be57d34fb2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QE Automation Architect</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Everbank</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa7e50031b6efc0</t>
+          <t>https://www.indeed.com/viewjob?jk=18e899cdb3d7157c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior IT Applications Engineer</t>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,3447 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4029cdbf9ce53a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99139af7425e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Distributed Systems)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41132f5995533032</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Vancouver, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=680eaf297b4a3a1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9ca72df2eb1613e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2440448cdb916bbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Modeling &amp; Data Governance Senior Consultant - Global Employer Services Technology</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Redshift, Data Lake, Git, Snowflake, Databricks, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20b0cbddccd952bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Capgemini Invent - Contextual Systems Engineer Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Atlanta, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Git, Snowflake, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73fdcada3159e500</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Central Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1cd60dbc92b91f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DevOps Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Origami Risk LLC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41fb38294434e54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Advanced Analytics and Insights</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4b37aaa551a8153</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Redshift, Data Lake, Snowflake, Databricks, Redshift, PySpark, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c600b5945ce8ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>UserGems</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, AKS, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc9835c6151bce1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c364e6657a4e5c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae7a3bc3505c24ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0308710711d9fc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5b35778c06f682d</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be7372bc771b0cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=473b5f755bec69af</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fb84fccd45f1b2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d454b040880c108</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00ea7d9e4d49ea45</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1d63c67aeabdc7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a835785437b33156</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=007eb750c2feb2d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=247dcabcfb9c3923</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ad2f643bdc49a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae9c13dce1ea3b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4451ae3681fdedd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1231dbf7bb428d53</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=736276cfe4dc14ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=822d06ac910abb85</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26679907d0cd2c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbe9955f440d88ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bae3f391e65591b</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50f0d6a9d029e17e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2f2bbb26a26fef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0527fb1fab98047f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=082aa13862c32a51</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05d20580ccc0b96a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35791602b31738af</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ced2fec132c10041</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abaa838922a1ee8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0910dff1a577f0b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dd86d44748fd8e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=509e6589bfb1d31e</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a6aa9622564cce</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07a33ee3bb438f2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a4582075a821476</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bfe9acf63e00541</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e741b0f1e8a88b58</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85c19f358ee522fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3924825325b3e164</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a9b71c5568fef75</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94beb83433c57e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ea91ad1354424de</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09e4ccfda6f6125c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a9e65e7bbf7fea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e939140a3f1c6d97</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87123856c93fd7ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68701317ae9410e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9f6cde55c8ee6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15f963188e117617</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cac218953fe60ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e8c449abd2f7965</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e66dabc0146e3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c31524087057570d</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b085bc2b76a1994a</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=201f3d774eca7669</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b20557c301b0ef1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5d4cb967b5d93d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5b1cdc635b21cf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4300a535e5cb926b</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3b429bd1d69ac25</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd882a948af06e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4c5068c9c1005de</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=582e627e5d2208b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3b97273aa8f2208</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a994b7bb46c3f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fd6d71976012059</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6c84c5f9cb52544</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b183fe040894a22c</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2a642cdb68a6555</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917cbf8f9bdb3636</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66ed09a75116cbce</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a0eb21a0e776691</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d18cf4ccc4b3743</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a24e70ad45a1c724</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d84d85809c3d2675</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2f479490ca46a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=123dc8a8caebd60e</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Encore Program</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f38e3f25e7d3506e</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Java Software Engineer I - Full-Stack - Financial Crimes</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f96178d920559bc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Terraform, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bfba46a758bb1aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Corpay</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Peachtree Corners, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7f53a2a0cc5ea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Fellow, AI Performance Software Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92cf1b446459dd15</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Jenkins, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885f6a06dd1ad29d</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=871ff43f4865fa34</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71d840cb6b082e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Crisis Prevention Institute</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea078764844575f8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-11.xlsx
+++ b/daily_matches/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer/Associate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>Seattle Children's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Mistral, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186c30600549672d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Financial Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Mistral, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d9122f4217ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=9dda4e17d3658df2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Architect– MediaOS Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Mistral, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89a2c7c81a4bcf04</t>
+          <t>https://www.indeed.com/viewjob?jk=76fdf46a06411390</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Architect– MediaOS Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Mistral, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8a8240038e2f312</t>
+          <t>https://www.indeed.com/viewjob?jk=f08935a87f5dd885</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Mistral, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4bd32d03cbba568</t>
+          <t>https://www.indeed.com/viewjob?jk=3080d0a12f64aa34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Kinesis, CI/CD, Git, Snowflake, Kafka, Tableau, Power BI, Python</t>
+          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, MongoDB, Cassandra, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N-iX</t>
+          <t>RecruitFox</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, Terraform, Git, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0084f621339b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f119c975697c8dbb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer (Corp Functions &amp; Supply Chain)</t>
+          <t>Data Engineer-Marketing Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foxit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Git, Databricks, Python, R</t>
+          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad1fee6cb0e2d10</t>
+          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Artificial Analysis</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, PyTorch, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0a719d5a6c6f30</t>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fd19f90ba79866</t>
+          <t>https://www.indeed.com/viewjob?jk=9d09a1b90b86ef4e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Platform Distinguished Engineer</t>
+          <t>Machine Learning Research Engineer (Scientific &amp; Engineering AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Optimal Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, PostgreSQL, MongoDB, NoSQL, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, Docker, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e670577c05d71c23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Infrastructure and DevOps Engineer</t>
+          <t>AI/ML Internship 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Onto Innovation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,38 +867,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253e640fb6d95154</t>
+          <t>https://www.indeed.com/viewjob?jk=5bed0dfe4b8ad465</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Applied AI ML Engineer Associate</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, PyTorch, XGBoost, MLflow, Git, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d2f09f1c484e2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=33fd91860b76c479</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Data &amp; Cloud Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Desmata Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New Paltz, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Databricks, PySpark, Hadoop, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a66201b7981fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=725665c443e0b9b8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Scientist GenAI</t>
+          <t>Senior Software Engineer - Autonomous Driving Simulation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>Generative AI, PyTorch, Docker, CI/CD, Jenkins, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1505650d64d0304a</t>
+          <t>https://www.indeed.com/viewjob?jk=82ded491222a54b5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>SRE/Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
+          <t>Tekcogno</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9277248c547d05a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9c88c99510ca87</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Hyperfleet -Maestro</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, Tableau, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afdda83a6ec944b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8963c96f2bc7f79</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hadoop, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, Tableau, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,252 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Engineer (R&amp;D)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=769a54c44af59c72</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Infrastructure Architect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Banner Life Family of Companies</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Frederick, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=911ba1a2c9202690</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Junior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Targeted Victory</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=832f7be458b3699c</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (AI Orchestrator)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb71a212b4cca14e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Python, AWS, GenAI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cff867b38b304182</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Salesforce Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Upstate Coin &amp; Gold</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Centennial, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=249b5dbf0c602cb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe82690704e0693</t>
+          <t>https://www.indeed.com/viewjob?jk=56353f45fe04818c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-11.xlsx
+++ b/daily_matches/job_matches_2026-06-11.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer/Associate</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Seattle Children's</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
+          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, Financial Platform</t>
+          <t>Sr. SW Engineer - Gen AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dda4e17d3658df2</t>
+          <t>https://www.indeed.com/viewjob?jk=1884f29272a6fa4d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Architect– MediaOS Platform</t>
+          <t>Software Engineer (Python / React)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Solution Design Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76fdf46a06411390</t>
+          <t>https://www.indeed.com/viewjob?jk=570a47973a523cb2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Architect– MediaOS Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, S3, Apache Airflow, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08935a87f5dd885</t>
+          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3080d0a12f64aa34</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Walkme</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, MongoDB, Cassandra, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
+          <t>https://www.indeed.com/viewjob?jk=1af1cdb9613b93fd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RecruitFox</t>
+          <t>Expel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f119c975697c8dbb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9e1dbdb4c0e170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer-Marketing Technology</t>
+          <t>Sr. AI &amp; Data Engineer–Trading Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foxit</t>
+          <t>Shell Energy Retail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PySpark, Python, SQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, MLflow, CI/CD, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
+          <t>https://www.indeed.com/viewjob?jk=f379cc52c6dc1b7b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
+          <t>Java springboot developer - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5a69cdd393ce38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Senior AI or ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d09a1b90b86ef4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4400b0b2feb031</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Research Engineer (Scientific &amp; Engineering AI)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optimal Inc.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Docker, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, Kubernetes, Kafka, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e670577c05d71c23</t>
+          <t>https://www.indeed.com/viewjob?jk=2417e3aa2741c89a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Internship 2</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Onto Innovation</t>
+          <t>Agile Defense</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bed0dfe4b8ad465</t>
+          <t>https://www.indeed.com/viewjob?jk=6621536db3bd9539</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, XGBoost, MLflow, Git, Python, SQL, R, Bayesian</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33fd91860b76c479</t>
+          <t>https://www.indeed.com/viewjob?jk=d185d79c2b670693</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer - Salesforce CRM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Desmata Inc</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Paltz, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Copilot, CI/CD, Git, MongoDB, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725665c443e0b9b8</t>
+          <t>https://www.indeed.com/viewjob?jk=286140a3d8c563f7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Autonomous Driving Simulation</t>
+          <t>Epic Cloud Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Southeast Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dothan, AL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, PyTorch, Docker, CI/CD, Jenkins, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ded491222a54b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0deb15ff717ae38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SRE/Azure DevOps Engineer</t>
+          <t>Software Engineer, Investor and Fund Administration Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tekcogno</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9c88c99510ca87</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1804190413e4d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Tableau, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8963c96f2bc7f79</t>
+          <t>https://www.indeed.com/viewjob?jk=f80cdc01bcc9fd94</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Tableau, Python, SQL, R, Scala, Bayesian, A/B Testing</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56353f45fe04818c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f97071c81152ea9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-11.xlsx
+++ b/daily_matches/job_matches_2026-06-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Generative AI Engineer, Officer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa52f2f8df5bbcb5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer - Gen AI</t>
+          <t>Data Engineer - Bilingual Mandarin required</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884f29272a6fa4d</t>
+          <t>https://www.indeed.com/viewjob?jk=bda129dc1d7139ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer (Python / React)</t>
+          <t>Data Engineer - Bilingual Mandarin required</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Solution Design Group</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=570a47973a523cb2</t>
+          <t>https://www.indeed.com/viewjob?jk=718307efaaa14959</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Apache Airflow, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, S3, EC2, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI/ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, PostgreSQL, Power BI, Python</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, Keras, S3, EC2, Redshift, Data Lake, MLflow, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1460aeeac19aef46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Copilot, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af1cdb9613b93fd</t>
+          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Expel</t>
+          <t>Riot Platforms, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Matplotlib, Seaborn, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca9e1dbdb4c0e170</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. AI &amp; Data Engineer–Trading Analytics</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shell Energy Retail</t>
+          <t>MEDecision</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, MLflow, CI/CD, Git, Databricks, PySpark, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Apache Airflow, CI/CD, Git, BigQuery, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f379cc52c6dc1b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java springboot developer - Senior Software Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5a69cdd393ce38</t>
+          <t>https://www.indeed.com/viewjob?jk=47abd28c0aa248a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI or ML Engineer - Remote</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4400b0b2feb031</t>
+          <t>https://www.indeed.com/viewjob?jk=973ffbc88d0c427a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Kubernetes, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2417e3aa2741c89a</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf0524e41351a6c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agile Defense</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6621536db3bd9539</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c9d41b3a88a9c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, MySQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185d79c2b670693</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer - Salesforce CRM Engineer</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MongoDB, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, BigQuery, Kubernetes, CI/CD, Terraform, Git, Snowflake, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286140a3d8c563f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Epic Cloud Administrator</t>
+          <t>Full Stack Java &amp; React Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Southeast Health</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dothan, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0deb15ff717ae38</t>
+          <t>https://www.indeed.com/viewjob?jk=b088c437f81d3a57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, Investor and Fund Administration Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1804190413e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,3122 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80cdc01bcc9fd94</t>
+          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hazleton, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Owosso, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Crown Point, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pinehurst, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Florence, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ashland, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Akumin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, BigQuery, Docker, Snowflake, BigQuery, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CarMax</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c27d2b7709f8adbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Associate Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Git, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AssetMark</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Snowflake, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Python Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hitapps</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, S3, FastAPI, Docker, CI/CD, Kafka, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cfc151f9ef1f70a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Data Sciences</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e18c43c72fcdf95d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pie Insurance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81175a9ea43e9f19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer - Platform</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GALAXY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Glue, Kubernetes, CI/CD, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c3b7bbd782d5471</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Azure ML, Synapse, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=822bd7aeae851aef</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer 3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4113b42887a4bc66</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Resideo</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MongoDB, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17e3196195f24fb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Health-Tech SaaS)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Phamily</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88f8c0bdd479674f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Performance Advertising Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PubMatic</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Kafka, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd5f4966ce9dd217</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (Manufacturing)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ion Storage Systems</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Beltsville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, Docker, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Ansible Automation &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef675551596020dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Associate Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ingram Micro</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20df3be8536f8fd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c847cdf8e486a8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - AI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3eab9bf177b59cda</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Elsevier</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64b2d48e82e7bf8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Elsevier</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32d3198ac6acbb60</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b90debc430ad885d</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e17d82fd1144d64</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b6bd1c44d43f512</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27caddedcbde04b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5711faa6fd8ebed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7106893d1c9ec84</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7e62b7be1516170</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29fa95cc19e6edd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15de7adfe73ee9a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec49b611d9bc27ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7271c523ab741fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=118d1b201f4ccb87</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2856ef2e511cd493</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f1c80888cfe8662</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=924f88aa54ab9a15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1372155a034d29e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfead2cdf6a14b3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73c2479e31ffa53d</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f896c0390ff4e21</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b2052e4a6d38432</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5ded6bdbfd1248</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=331b45849dd26fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3659bc1e9b767292</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d062fac886ad0b9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc53a5fdf75e745</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=697c7423d3d4ff47</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a14eeba16fc1af25</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50d2dc37cd4cd152</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59357e7bb864edc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d099a5ec928276a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=294dc3643ef230c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0cc6b7533ff0862</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38fda2e91a485fcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e9755bf829b7878</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27be4d00e48c8773</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bda2ec00d253d51d</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e080d81aab7752</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d23934e5dda17655</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=952e429f9e9be0c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52735c73667d3f55</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5bf2a88eea61519</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=749d122eaea7d203</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1fb499916faa32c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8bf5efbba049afe</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31ea8275f722c36c</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9064cf60fd012cf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f83d02ca0099b592</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25a6dd97525904a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=324c31c58d684c81</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=635d59fc5183882d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Statistical Analyst</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mission Pet Health</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Bayesian, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66a15d299d6b42e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Network Security Lab Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f97071c81152ea9</t>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=926a8df50008757b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III: GraphQL Platform</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4447169b102a95ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>iOS Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=771d060156d096c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Databricks, PySpark, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c52b2e8afd502eac</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Liquid Property Group, LLC</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c920ecca65228ea5</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer- Remote</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Harbor Freight Tools</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Calabasas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e0c4b502a6bd1e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Scientist I - School of Public Health</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>UTHealth Houston</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Hadoop, Tableau, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6f2ffa048894b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>InterVenn Biosciences</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>South San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, LightGBM, Python, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04cd6963232d938f</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Global Banking &amp; Markets - New York - Associate, Quantitative Engineering - 4195191</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, MLflow, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a879eaf968b89280</t>
         </is>
       </c>
     </row>
